--- a/데이터 전처리/영경/missing_zero_report.xlsx
+++ b/데이터 전처리/영경/missing_zero_report.xlsx
@@ -455,13 +455,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>62077</v>
+        <v>62057</v>
       </c>
       <c r="C2" t="n">
         <v>32102</v>
       </c>
       <c r="D2" t="n">
-        <v>94179</v>
+        <v>94159</v>
       </c>
       <c r="E2" t="n">
         <v>65.91</v>
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C3" t="n">
         <v>94067</v>
       </c>
       <c r="D3" t="n">
-        <v>94180</v>
+        <v>94160</v>
       </c>
       <c r="E3" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>99.88</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62077</v>
+        <v>62057</v>
       </c>
       <c r="C4" t="n">
         <v>32103</v>
       </c>
       <c r="D4" t="n">
-        <v>94180</v>
+        <v>94160</v>
       </c>
       <c r="E4" t="n">
         <v>65.91</v>
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C5" t="n">
         <v>94067</v>
       </c>
       <c r="D5" t="n">
-        <v>94180</v>
+        <v>94160</v>
       </c>
       <c r="E5" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>99.88</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -555,19 +555,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C6" t="n">
         <v>94062</v>
       </c>
       <c r="D6" t="n">
-        <v>94175</v>
+        <v>94155</v>
       </c>
       <c r="E6" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F6" t="n">
-        <v>99.87</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>99.98999999999999</v>
@@ -580,19 +580,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
         <v>94021</v>
       </c>
       <c r="D7" t="n">
-        <v>94134</v>
+        <v>94114</v>
       </c>
       <c r="E7" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F7" t="n">
-        <v>99.83</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>99.95</v>
@@ -605,19 +605,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
         <v>94011</v>
       </c>
       <c r="D8" t="n">
-        <v>94124</v>
+        <v>94104</v>
       </c>
       <c r="E8" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F8" t="n">
-        <v>99.81999999999999</v>
+        <v>99.84</v>
       </c>
       <c r="G8" t="n">
         <v>99.94</v>
@@ -630,19 +630,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C9" t="n">
         <v>93882</v>
       </c>
       <c r="D9" t="n">
-        <v>93995</v>
+        <v>93975</v>
       </c>
       <c r="E9" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F9" t="n">
-        <v>99.68000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="G9" t="n">
         <v>99.8</v>
@@ -655,19 +655,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C10" t="n">
         <v>93836</v>
       </c>
       <c r="D10" t="n">
-        <v>93949</v>
+        <v>93929</v>
       </c>
       <c r="E10" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F10" t="n">
-        <v>99.63</v>
+        <v>99.66</v>
       </c>
       <c r="G10" t="n">
         <v>99.75</v>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C11" t="n">
         <v>93771</v>
       </c>
       <c r="D11" t="n">
-        <v>93884</v>
+        <v>93864</v>
       </c>
       <c r="E11" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F11" t="n">
-        <v>99.56999999999999</v>
+        <v>99.59</v>
       </c>
       <c r="G11" t="n">
         <v>99.69</v>
@@ -705,19 +705,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C12" t="n">
         <v>93725</v>
       </c>
       <c r="D12" t="n">
-        <v>93838</v>
+        <v>93818</v>
       </c>
       <c r="E12" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F12" t="n">
-        <v>99.52</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>99.64</v>
@@ -730,19 +730,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C13" t="n">
         <v>93721</v>
       </c>
       <c r="D13" t="n">
-        <v>93834</v>
+        <v>93814</v>
       </c>
       <c r="E13" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F13" t="n">
-        <v>99.51000000000001</v>
+        <v>99.53</v>
       </c>
       <c r="G13" t="n">
         <v>99.63</v>
@@ -755,19 +755,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C14" t="n">
         <v>93633</v>
       </c>
       <c r="D14" t="n">
-        <v>93746</v>
+        <v>93726</v>
       </c>
       <c r="E14" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F14" t="n">
-        <v>99.42</v>
+        <v>99.44</v>
       </c>
       <c r="G14" t="n">
         <v>99.54000000000001</v>
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C15" t="n">
         <v>93632</v>
       </c>
       <c r="D15" t="n">
-        <v>93745</v>
+        <v>93725</v>
       </c>
       <c r="E15" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F15" t="n">
-        <v>99.42</v>
+        <v>99.44</v>
       </c>
       <c r="G15" t="n">
         <v>99.54000000000001</v>
@@ -805,19 +805,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C16" t="n">
         <v>93398</v>
       </c>
       <c r="D16" t="n">
-        <v>93511</v>
+        <v>93491</v>
       </c>
       <c r="E16" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F16" t="n">
-        <v>99.17</v>
+        <v>99.19</v>
       </c>
       <c r="G16" t="n">
         <v>99.29000000000001</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C17" t="n">
         <v>92967</v>
       </c>
       <c r="D17" t="n">
-        <v>93080</v>
+        <v>93060</v>
       </c>
       <c r="E17" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F17" t="n">
-        <v>98.70999999999999</v>
+        <v>98.73</v>
       </c>
       <c r="G17" t="n">
         <v>98.83</v>
@@ -855,19 +855,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C18" t="n">
         <v>92096</v>
       </c>
       <c r="D18" t="n">
-        <v>92209</v>
+        <v>92189</v>
       </c>
       <c r="E18" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F18" t="n">
-        <v>97.79000000000001</v>
+        <v>97.81</v>
       </c>
       <c r="G18" t="n">
         <v>97.91</v>
@@ -880,19 +880,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C19" t="n">
         <v>91615</v>
       </c>
       <c r="D19" t="n">
-        <v>91728</v>
+        <v>91708</v>
       </c>
       <c r="E19" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F19" t="n">
-        <v>97.28</v>
+        <v>97.3</v>
       </c>
       <c r="G19" t="n">
         <v>97.40000000000001</v>
@@ -905,19 +905,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C20" t="n">
         <v>90978</v>
       </c>
       <c r="D20" t="n">
-        <v>91091</v>
+        <v>91071</v>
       </c>
       <c r="E20" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F20" t="n">
-        <v>96.59999999999999</v>
+        <v>96.62</v>
       </c>
       <c r="G20" t="n">
         <v>96.72</v>
@@ -930,19 +930,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C21" t="n">
         <v>90521</v>
       </c>
       <c r="D21" t="n">
-        <v>90634</v>
+        <v>90614</v>
       </c>
       <c r="E21" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F21" t="n">
-        <v>96.11</v>
+        <v>96.14</v>
       </c>
       <c r="G21" t="n">
         <v>96.23</v>
@@ -955,19 +955,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C22" t="n">
         <v>90291</v>
       </c>
       <c r="D22" t="n">
-        <v>90404</v>
+        <v>90384</v>
       </c>
       <c r="E22" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F22" t="n">
-        <v>95.87</v>
+        <v>95.89</v>
       </c>
       <c r="G22" t="n">
         <v>95.98999999999999</v>
@@ -980,22 +980,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C23" t="n">
         <v>90107</v>
       </c>
       <c r="D23" t="n">
-        <v>90220</v>
+        <v>90200</v>
       </c>
       <c r="E23" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F23" t="n">
-        <v>95.68000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="G23" t="n">
-        <v>95.8</v>
+        <v>95.79000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C24" t="n">
         <v>90054</v>
       </c>
       <c r="D24" t="n">
-        <v>90167</v>
+        <v>90147</v>
       </c>
       <c r="E24" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F24" t="n">
-        <v>95.62</v>
+        <v>95.64</v>
       </c>
       <c r="G24" t="n">
         <v>95.73999999999999</v>
@@ -1030,19 +1030,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C25" t="n">
         <v>88551</v>
       </c>
       <c r="D25" t="n">
-        <v>88664</v>
+        <v>88644</v>
       </c>
       <c r="E25" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F25" t="n">
-        <v>94.02</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>94.14</v>
@@ -1058,10 +1058,10 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>88482</v>
+        <v>88462</v>
       </c>
       <c r="D26" t="n">
-        <v>88482</v>
+        <v>88462</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1080,22 +1080,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C27" t="n">
         <v>87225</v>
       </c>
       <c r="D27" t="n">
-        <v>87338</v>
+        <v>87318</v>
       </c>
       <c r="E27" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F27" t="n">
-        <v>92.62</v>
+        <v>92.63</v>
       </c>
       <c r="G27" t="n">
-        <v>92.73999999999999</v>
+        <v>92.73</v>
       </c>
     </row>
     <row r="28">
@@ -1105,22 +1105,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C28" t="n">
         <v>87075</v>
       </c>
       <c r="D28" t="n">
-        <v>87188</v>
+        <v>87168</v>
       </c>
       <c r="E28" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F28" t="n">
-        <v>92.45999999999999</v>
+        <v>92.48</v>
       </c>
       <c r="G28" t="n">
-        <v>92.58</v>
+        <v>92.56999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1130,19 +1130,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C29" t="n">
         <v>87033</v>
       </c>
       <c r="D29" t="n">
-        <v>87146</v>
+        <v>87126</v>
       </c>
       <c r="E29" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F29" t="n">
-        <v>92.41</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>92.53</v>
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C30" t="n">
         <v>87014</v>
       </c>
       <c r="D30" t="n">
-        <v>87127</v>
+        <v>87107</v>
       </c>
       <c r="E30" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F30" t="n">
-        <v>92.39</v>
+        <v>92.41</v>
       </c>
       <c r="G30" t="n">
         <v>92.51000000000001</v>
@@ -1180,19 +1180,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C31" t="n">
         <v>84784</v>
       </c>
       <c r="D31" t="n">
-        <v>84897</v>
+        <v>84877</v>
       </c>
       <c r="E31" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F31" t="n">
-        <v>90.02</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="G31" t="n">
         <v>90.14</v>
@@ -1205,19 +1205,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C32" t="n">
         <v>84489</v>
       </c>
       <c r="D32" t="n">
-        <v>84602</v>
+        <v>84582</v>
       </c>
       <c r="E32" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F32" t="n">
-        <v>89.70999999999999</v>
+        <v>89.73</v>
       </c>
       <c r="G32" t="n">
         <v>89.83</v>
@@ -1230,19 +1230,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C33" t="n">
         <v>83165</v>
       </c>
       <c r="D33" t="n">
-        <v>83278</v>
+        <v>83258</v>
       </c>
       <c r="E33" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F33" t="n">
-        <v>88.3</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="G33" t="n">
         <v>88.42</v>
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C34" t="n">
         <v>81957</v>
       </c>
       <c r="D34" t="n">
-        <v>82070</v>
+        <v>82050</v>
       </c>
       <c r="E34" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F34" t="n">
-        <v>87.02</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="G34" t="n">
         <v>87.14</v>
@@ -1280,22 +1280,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C35" t="n">
         <v>78506</v>
       </c>
       <c r="D35" t="n">
-        <v>78619</v>
+        <v>78599</v>
       </c>
       <c r="E35" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F35" t="n">
-        <v>83.36</v>
+        <v>83.38</v>
       </c>
       <c r="G35" t="n">
-        <v>83.48</v>
+        <v>83.47</v>
       </c>
     </row>
     <row r="36">
@@ -1305,19 +1305,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C36" t="n">
         <v>76921</v>
       </c>
       <c r="D36" t="n">
-        <v>77034</v>
+        <v>77014</v>
       </c>
       <c r="E36" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F36" t="n">
-        <v>81.67</v>
+        <v>81.69</v>
       </c>
       <c r="G36" t="n">
         <v>81.79000000000001</v>
@@ -1330,19 +1330,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C37" t="n">
         <v>76542</v>
       </c>
       <c r="D37" t="n">
-        <v>76655</v>
+        <v>76635</v>
       </c>
       <c r="E37" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F37" t="n">
-        <v>81.27</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="G37" t="n">
         <v>81.39</v>
@@ -1355,19 +1355,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C38" t="n">
         <v>76347</v>
       </c>
       <c r="D38" t="n">
-        <v>76460</v>
+        <v>76440</v>
       </c>
       <c r="E38" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F38" t="n">
-        <v>81.06</v>
+        <v>81.08</v>
       </c>
       <c r="G38" t="n">
         <v>81.18000000000001</v>
@@ -1380,19 +1380,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C39" t="n">
         <v>74009</v>
       </c>
       <c r="D39" t="n">
-        <v>74122</v>
+        <v>74102</v>
       </c>
       <c r="E39" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F39" t="n">
-        <v>78.58</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G39" t="n">
         <v>78.7</v>
@@ -1405,19 +1405,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C40" t="n">
         <v>73615</v>
       </c>
       <c r="D40" t="n">
-        <v>73728</v>
+        <v>73708</v>
       </c>
       <c r="E40" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F40" t="n">
-        <v>78.16</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="G40" t="n">
         <v>78.28</v>
@@ -1430,19 +1430,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C41" t="n">
         <v>71221</v>
       </c>
       <c r="D41" t="n">
-        <v>71334</v>
+        <v>71314</v>
       </c>
       <c r="E41" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F41" t="n">
-        <v>75.62</v>
+        <v>75.64</v>
       </c>
       <c r="G41" t="n">
         <v>75.73999999999999</v>
@@ -1455,22 +1455,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C42" t="n">
         <v>69579</v>
       </c>
       <c r="D42" t="n">
-        <v>69692</v>
+        <v>69672</v>
       </c>
       <c r="E42" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F42" t="n">
-        <v>73.88</v>
+        <v>73.89</v>
       </c>
       <c r="G42" t="n">
-        <v>74</v>
+        <v>73.98999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -1480,19 +1480,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C43" t="n">
         <v>67529</v>
       </c>
       <c r="D43" t="n">
-        <v>67642</v>
+        <v>67622</v>
       </c>
       <c r="E43" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F43" t="n">
-        <v>71.7</v>
+        <v>71.72</v>
       </c>
       <c r="G43" t="n">
         <v>71.81999999999999</v>
@@ -1505,19 +1505,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C44" t="n">
         <v>65374</v>
       </c>
       <c r="D44" t="n">
-        <v>65487</v>
+        <v>65467</v>
       </c>
       <c r="E44" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F44" t="n">
-        <v>69.41</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="G44" t="n">
         <v>69.53</v>
@@ -1530,19 +1530,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C45" t="n">
         <v>65262</v>
       </c>
       <c r="D45" t="n">
-        <v>65375</v>
+        <v>65355</v>
       </c>
       <c r="E45" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F45" t="n">
-        <v>69.29000000000001</v>
+        <v>69.31</v>
       </c>
       <c r="G45" t="n">
         <v>69.41</v>
@@ -1555,19 +1555,19 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C46" t="n">
         <v>64628</v>
       </c>
       <c r="D46" t="n">
-        <v>64741</v>
+        <v>64721</v>
       </c>
       <c r="E46" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F46" t="n">
-        <v>68.62</v>
+        <v>68.64</v>
       </c>
       <c r="G46" t="n">
         <v>68.73999999999999</v>
@@ -1580,22 +1580,22 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C47" t="n">
         <v>62846</v>
       </c>
       <c r="D47" t="n">
-        <v>62959</v>
+        <v>62939</v>
       </c>
       <c r="E47" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F47" t="n">
-        <v>66.73</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>66.84999999999999</v>
+        <v>66.84</v>
       </c>
     </row>
     <row r="48">
@@ -1605,19 +1605,19 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C48" t="n">
         <v>59016</v>
       </c>
       <c r="D48" t="n">
-        <v>59129</v>
+        <v>59109</v>
       </c>
       <c r="E48" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F48" t="n">
-        <v>62.66</v>
+        <v>62.68</v>
       </c>
       <c r="G48" t="n">
         <v>62.78</v>
@@ -1630,22 +1630,22 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C49" t="n">
         <v>56780</v>
       </c>
       <c r="D49" t="n">
-        <v>56893</v>
+        <v>56873</v>
       </c>
       <c r="E49" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F49" t="n">
-        <v>60.29</v>
+        <v>60.3</v>
       </c>
       <c r="G49" t="n">
-        <v>60.41</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="50">
@@ -1655,22 +1655,22 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C50" t="n">
         <v>56438</v>
       </c>
       <c r="D50" t="n">
-        <v>56551</v>
+        <v>56531</v>
       </c>
       <c r="E50" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F50" t="n">
-        <v>59.93</v>
+        <v>59.94</v>
       </c>
       <c r="G50" t="n">
-        <v>60.05</v>
+        <v>60.04</v>
       </c>
     </row>
     <row r="51">
@@ -1680,22 +1680,22 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C51" t="n">
         <v>51120</v>
       </c>
       <c r="D51" t="n">
-        <v>51233</v>
+        <v>51213</v>
       </c>
       <c r="E51" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F51" t="n">
-        <v>54.28</v>
+        <v>54.29</v>
       </c>
       <c r="G51" t="n">
-        <v>54.4</v>
+        <v>54.39</v>
       </c>
     </row>
     <row r="52">
@@ -1705,22 +1705,22 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C52" t="n">
         <v>50917</v>
       </c>
       <c r="D52" t="n">
-        <v>51030</v>
+        <v>51010</v>
       </c>
       <c r="E52" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F52" t="n">
-        <v>54.06</v>
+        <v>54.07</v>
       </c>
       <c r="G52" t="n">
-        <v>54.18</v>
+        <v>54.17</v>
       </c>
     </row>
     <row r="53">
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C53" t="n">
         <v>50862</v>
       </c>
       <c r="D53" t="n">
-        <v>50975</v>
+        <v>50955</v>
       </c>
       <c r="E53" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F53" t="n">
-        <v>54.01</v>
+        <v>54.02</v>
       </c>
       <c r="G53" t="n">
-        <v>54.13</v>
+        <v>54.12</v>
       </c>
     </row>
     <row r="54">
@@ -1755,22 +1755,22 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C54" t="n">
         <v>48702</v>
       </c>
       <c r="D54" t="n">
-        <v>48815</v>
+        <v>48795</v>
       </c>
       <c r="E54" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F54" t="n">
-        <v>51.71</v>
+        <v>51.72</v>
       </c>
       <c r="G54" t="n">
-        <v>51.83</v>
+        <v>51.82</v>
       </c>
     </row>
     <row r="55">
@@ -1780,22 +1780,22 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C55" t="n">
         <v>47832</v>
       </c>
       <c r="D55" t="n">
-        <v>47945</v>
+        <v>47925</v>
       </c>
       <c r="E55" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F55" t="n">
-        <v>50.79</v>
+        <v>50.8</v>
       </c>
       <c r="G55" t="n">
-        <v>50.91</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="56">
@@ -1805,22 +1805,22 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C56" t="n">
         <v>46757</v>
       </c>
       <c r="D56" t="n">
-        <v>46870</v>
+        <v>46850</v>
       </c>
       <c r="E56" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F56" t="n">
-        <v>49.65</v>
+        <v>49.66</v>
       </c>
       <c r="G56" t="n">
-        <v>49.77</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="57">
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C57" t="n">
         <v>46338</v>
       </c>
       <c r="D57" t="n">
-        <v>46451</v>
+        <v>46431</v>
       </c>
       <c r="E57" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F57" t="n">
-        <v>49.2</v>
+        <v>49.21</v>
       </c>
       <c r="G57" t="n">
-        <v>49.32</v>
+        <v>49.31</v>
       </c>
     </row>
     <row r="58">
@@ -1855,22 +1855,22 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C58" t="n">
         <v>44328</v>
       </c>
       <c r="D58" t="n">
-        <v>44441</v>
+        <v>44421</v>
       </c>
       <c r="E58" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F58" t="n">
-        <v>47.07</v>
+        <v>47.08</v>
       </c>
       <c r="G58" t="n">
-        <v>47.19</v>
+        <v>47.18</v>
       </c>
     </row>
     <row r="59">
@@ -1880,22 +1880,22 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C59" t="n">
         <v>43990</v>
       </c>
       <c r="D59" t="n">
-        <v>44103</v>
+        <v>44083</v>
       </c>
       <c r="E59" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F59" t="n">
-        <v>46.71</v>
+        <v>46.72</v>
       </c>
       <c r="G59" t="n">
-        <v>46.83</v>
+        <v>46.82</v>
       </c>
     </row>
     <row r="60">
@@ -1905,22 +1905,22 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C60" t="n">
         <v>43901</v>
       </c>
       <c r="D60" t="n">
-        <v>44014</v>
+        <v>43994</v>
       </c>
       <c r="E60" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F60" t="n">
-        <v>46.61</v>
+        <v>46.62</v>
       </c>
       <c r="G60" t="n">
-        <v>46.73</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="61">
@@ -1930,22 +1930,22 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C61" t="n">
         <v>41192</v>
       </c>
       <c r="D61" t="n">
-        <v>41305</v>
+        <v>41285</v>
       </c>
       <c r="E61" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F61" t="n">
-        <v>43.74</v>
+        <v>43.75</v>
       </c>
       <c r="G61" t="n">
-        <v>43.86</v>
+        <v>43.85</v>
       </c>
     </row>
     <row r="62">
@@ -1955,22 +1955,22 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C62" t="n">
         <v>39653</v>
       </c>
       <c r="D62" t="n">
-        <v>39766</v>
+        <v>39746</v>
       </c>
       <c r="E62" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F62" t="n">
-        <v>42.1</v>
+        <v>42.11</v>
       </c>
       <c r="G62" t="n">
-        <v>42.22</v>
+        <v>42.21</v>
       </c>
     </row>
     <row r="63">
@@ -1980,22 +1980,22 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C63" t="n">
         <v>38550</v>
       </c>
       <c r="D63" t="n">
-        <v>38663</v>
+        <v>38643</v>
       </c>
       <c r="E63" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F63" t="n">
-        <v>40.93</v>
+        <v>40.94</v>
       </c>
       <c r="G63" t="n">
-        <v>41.05</v>
+        <v>41.04</v>
       </c>
     </row>
     <row r="64">
@@ -2005,22 +2005,22 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C64" t="n">
         <v>32743</v>
       </c>
       <c r="D64" t="n">
-        <v>32856</v>
+        <v>32836</v>
       </c>
       <c r="E64" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F64" t="n">
         <v>34.77</v>
       </c>
       <c r="G64" t="n">
-        <v>34.89</v>
+        <v>34.87</v>
       </c>
     </row>
     <row r="65">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C65" t="n">
         <v>32718</v>
       </c>
       <c r="D65" t="n">
-        <v>32831</v>
+        <v>32811</v>
       </c>
       <c r="E65" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F65" t="n">
-        <v>34.74</v>
+        <v>34.75</v>
       </c>
       <c r="G65" t="n">
-        <v>34.86</v>
+        <v>34.85</v>
       </c>
     </row>
     <row r="66">
@@ -2055,22 +2055,22 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C66" t="n">
         <v>32061</v>
       </c>
       <c r="D66" t="n">
-        <v>32174</v>
+        <v>32154</v>
       </c>
       <c r="E66" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F66" t="n">
-        <v>34.04</v>
+        <v>34.05</v>
       </c>
       <c r="G66" t="n">
-        <v>34.16</v>
+        <v>34.15</v>
       </c>
     </row>
     <row r="67">
@@ -2080,22 +2080,22 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C67" t="n">
         <v>31601</v>
       </c>
       <c r="D67" t="n">
-        <v>31714</v>
+        <v>31694</v>
       </c>
       <c r="E67" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F67" t="n">
-        <v>33.55</v>
+        <v>33.56</v>
       </c>
       <c r="G67" t="n">
-        <v>33.67</v>
+        <v>33.66</v>
       </c>
     </row>
     <row r="68">
@@ -2105,22 +2105,22 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C68" t="n">
         <v>30671</v>
       </c>
       <c r="D68" t="n">
-        <v>30784</v>
+        <v>30764</v>
       </c>
       <c r="E68" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F68" t="n">
         <v>32.57</v>
       </c>
       <c r="G68" t="n">
-        <v>32.69</v>
+        <v>32.67</v>
       </c>
     </row>
     <row r="69">
@@ -2130,22 +2130,22 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C69" t="n">
         <v>27840</v>
       </c>
       <c r="D69" t="n">
-        <v>27953</v>
+        <v>27933</v>
       </c>
       <c r="E69" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F69" t="n">
-        <v>29.56</v>
+        <v>29.57</v>
       </c>
       <c r="G69" t="n">
-        <v>29.68</v>
+        <v>29.67</v>
       </c>
     </row>
     <row r="70">
@@ -2158,10 +2158,10 @@
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>27679</v>
+        <v>27669</v>
       </c>
       <c r="D70" t="n">
-        <v>27679</v>
+        <v>27669</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -2180,22 +2180,22 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C71" t="n">
         <v>27306</v>
       </c>
       <c r="D71" t="n">
-        <v>27419</v>
+        <v>27399</v>
       </c>
       <c r="E71" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F71" t="n">
-        <v>28.99</v>
+        <v>29</v>
       </c>
       <c r="G71" t="n">
-        <v>29.11</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="72">
@@ -2205,22 +2205,22 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C72" t="n">
         <v>25777</v>
       </c>
       <c r="D72" t="n">
-        <v>25890</v>
+        <v>25870</v>
       </c>
       <c r="E72" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F72" t="n">
-        <v>27.37</v>
+        <v>27.38</v>
       </c>
       <c r="G72" t="n">
-        <v>27.49</v>
+        <v>27.47</v>
       </c>
     </row>
     <row r="73">
@@ -2230,22 +2230,22 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C73" t="n">
         <v>23988</v>
       </c>
       <c r="D73" t="n">
-        <v>24101</v>
+        <v>24081</v>
       </c>
       <c r="E73" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F73" t="n">
-        <v>25.47</v>
+        <v>25.48</v>
       </c>
       <c r="G73" t="n">
-        <v>25.59</v>
+        <v>25.57</v>
       </c>
     </row>
     <row r="74">
@@ -2255,22 +2255,22 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C74" t="n">
         <v>23936</v>
       </c>
       <c r="D74" t="n">
-        <v>24049</v>
+        <v>24029</v>
       </c>
       <c r="E74" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F74" t="n">
         <v>25.42</v>
       </c>
       <c r="G74" t="n">
-        <v>25.54</v>
+        <v>25.52</v>
       </c>
     </row>
     <row r="75">
@@ -2280,22 +2280,22 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C75" t="n">
         <v>20852</v>
       </c>
       <c r="D75" t="n">
-        <v>20965</v>
+        <v>20945</v>
       </c>
       <c r="E75" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F75" t="n">
-        <v>22.14</v>
+        <v>22.15</v>
       </c>
       <c r="G75" t="n">
-        <v>22.26</v>
+        <v>22.24</v>
       </c>
     </row>
     <row r="76">
@@ -2305,22 +2305,22 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C76" t="n">
         <v>20650</v>
       </c>
       <c r="D76" t="n">
-        <v>20763</v>
+        <v>20743</v>
       </c>
       <c r="E76" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F76" t="n">
         <v>21.93</v>
       </c>
       <c r="G76" t="n">
-        <v>22.05</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="77">
@@ -2330,22 +2330,22 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C77" t="n">
         <v>20240</v>
       </c>
       <c r="D77" t="n">
-        <v>20353</v>
+        <v>20333</v>
       </c>
       <c r="E77" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F77" t="n">
-        <v>21.49</v>
+        <v>21.5</v>
       </c>
       <c r="G77" t="n">
-        <v>21.61</v>
+        <v>21.59</v>
       </c>
     </row>
     <row r="78">
@@ -2355,22 +2355,22 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C78" t="n">
         <v>20146</v>
       </c>
       <c r="D78" t="n">
-        <v>20259</v>
+        <v>20239</v>
       </c>
       <c r="E78" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F78" t="n">
-        <v>21.39</v>
+        <v>21.4</v>
       </c>
       <c r="G78" t="n">
-        <v>21.51</v>
+        <v>21.49</v>
       </c>
     </row>
     <row r="79">
@@ -2383,19 +2383,19 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>19124</v>
+        <v>19104</v>
       </c>
       <c r="D79" t="n">
-        <v>19124</v>
+        <v>19104</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>20.31</v>
+        <v>20.29</v>
       </c>
       <c r="G79" t="n">
-        <v>20.31</v>
+        <v>20.29</v>
       </c>
     </row>
     <row r="80">
@@ -2430,22 +2430,22 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C81" t="n">
         <v>18474</v>
       </c>
       <c r="D81" t="n">
-        <v>18587</v>
+        <v>18567</v>
       </c>
       <c r="E81" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F81" t="n">
         <v>19.62</v>
       </c>
       <c r="G81" t="n">
-        <v>19.74</v>
+        <v>19.72</v>
       </c>
     </row>
     <row r="82">
@@ -2455,22 +2455,22 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C82" t="n">
         <v>16891</v>
       </c>
       <c r="D82" t="n">
-        <v>17004</v>
+        <v>16984</v>
       </c>
       <c r="E82" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F82" t="n">
-        <v>17.93</v>
+        <v>17.94</v>
       </c>
       <c r="G82" t="n">
-        <v>18.05</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="83">
@@ -2480,22 +2480,22 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C83" t="n">
         <v>16395</v>
       </c>
       <c r="D83" t="n">
-        <v>16508</v>
+        <v>16488</v>
       </c>
       <c r="E83" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F83" t="n">
         <v>17.41</v>
       </c>
       <c r="G83" t="n">
-        <v>17.53</v>
+        <v>17.51</v>
       </c>
     </row>
     <row r="84">
@@ -2505,22 +2505,22 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C84" t="n">
         <v>16131</v>
       </c>
       <c r="D84" t="n">
-        <v>16244</v>
+        <v>16224</v>
       </c>
       <c r="E84" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F84" t="n">
         <v>17.13</v>
       </c>
       <c r="G84" t="n">
-        <v>17.25</v>
+        <v>17.23</v>
       </c>
     </row>
     <row r="85">
@@ -2530,22 +2530,22 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C85" t="n">
         <v>16068</v>
       </c>
       <c r="D85" t="n">
-        <v>16181</v>
+        <v>16161</v>
       </c>
       <c r="E85" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F85" t="n">
         <v>17.06</v>
       </c>
       <c r="G85" t="n">
-        <v>17.18</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="86">
@@ -2555,22 +2555,22 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C86" t="n">
         <v>14259</v>
       </c>
       <c r="D86" t="n">
-        <v>14372</v>
+        <v>14352</v>
       </c>
       <c r="E86" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F86" t="n">
         <v>15.14</v>
       </c>
       <c r="G86" t="n">
-        <v>15.26</v>
+        <v>15.24</v>
       </c>
     </row>
     <row r="87">
@@ -2580,22 +2580,22 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C87" t="n">
         <v>11853</v>
       </c>
       <c r="D87" t="n">
-        <v>11966</v>
+        <v>11946</v>
       </c>
       <c r="E87" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F87" t="n">
         <v>12.59</v>
       </c>
       <c r="G87" t="n">
-        <v>12.71</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="88">
@@ -2605,22 +2605,22 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C88" t="n">
         <v>10859</v>
       </c>
       <c r="D88" t="n">
-        <v>10972</v>
+        <v>10952</v>
       </c>
       <c r="E88" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F88" t="n">
         <v>11.53</v>
       </c>
       <c r="G88" t="n">
-        <v>11.65</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="89">
@@ -2630,22 +2630,22 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C89" t="n">
         <v>9778</v>
       </c>
       <c r="D89" t="n">
-        <v>9891</v>
+        <v>9871</v>
       </c>
       <c r="E89" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F89" t="n">
         <v>10.38</v>
       </c>
       <c r="G89" t="n">
-        <v>10.5</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="90">
@@ -2655,22 +2655,22 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C90" t="n">
         <v>9340</v>
       </c>
       <c r="D90" t="n">
-        <v>9453</v>
+        <v>9433</v>
       </c>
       <c r="E90" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F90" t="n">
         <v>9.92</v>
       </c>
       <c r="G90" t="n">
-        <v>10.04</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="91">
@@ -2680,22 +2680,22 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C91" t="n">
         <v>8683</v>
       </c>
       <c r="D91" t="n">
-        <v>8796</v>
+        <v>8776</v>
       </c>
       <c r="E91" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F91" t="n">
         <v>9.220000000000001</v>
       </c>
       <c r="G91" t="n">
-        <v>9.34</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="92">
@@ -2705,22 +2705,22 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C92" t="n">
         <v>8499</v>
       </c>
       <c r="D92" t="n">
-        <v>8612</v>
+        <v>8592</v>
       </c>
       <c r="E92" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F92" t="n">
-        <v>9.02</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G92" t="n">
-        <v>9.140000000000001</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="93">
@@ -2730,22 +2730,22 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C93" t="n">
         <v>7810</v>
       </c>
       <c r="D93" t="n">
-        <v>7923</v>
+        <v>7903</v>
       </c>
       <c r="E93" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F93" t="n">
         <v>8.289999999999999</v>
       </c>
       <c r="G93" t="n">
-        <v>8.41</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="94">
@@ -2755,22 +2755,22 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C94" t="n">
         <v>6406</v>
       </c>
       <c r="D94" t="n">
-        <v>6519</v>
+        <v>6499</v>
       </c>
       <c r="E94" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F94" t="n">
         <v>6.8</v>
       </c>
       <c r="G94" t="n">
-        <v>6.92</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="95">
@@ -2780,22 +2780,22 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C95" t="n">
         <v>5076</v>
       </c>
       <c r="D95" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="E95" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F95" t="n">
         <v>5.39</v>
       </c>
       <c r="G95" t="n">
-        <v>5.51</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="96">
@@ -2805,22 +2805,22 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C96" t="n">
         <v>4779</v>
       </c>
       <c r="D96" t="n">
-        <v>4892</v>
+        <v>4872</v>
       </c>
       <c r="E96" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F96" t="n">
-        <v>5.07</v>
+        <v>5.08</v>
       </c>
       <c r="G96" t="n">
-        <v>5.19</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="97">
@@ -2830,22 +2830,22 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C97" t="n">
         <v>4671</v>
       </c>
       <c r="D97" t="n">
-        <v>4784</v>
+        <v>4764</v>
       </c>
       <c r="E97" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F97" t="n">
         <v>4.96</v>
       </c>
       <c r="G97" t="n">
-        <v>5.08</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="98">
@@ -2855,22 +2855,22 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C98" t="n">
         <v>3727</v>
       </c>
       <c r="D98" t="n">
-        <v>3840</v>
+        <v>3820</v>
       </c>
       <c r="E98" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F98" t="n">
         <v>3.96</v>
       </c>
       <c r="G98" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="99">
@@ -2880,22 +2880,22 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C99" t="n">
         <v>3617</v>
       </c>
       <c r="D99" t="n">
-        <v>3730</v>
+        <v>3710</v>
       </c>
       <c r="E99" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F99" t="n">
         <v>3.84</v>
       </c>
       <c r="G99" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="100">
@@ -2905,22 +2905,22 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C100" t="n">
         <v>3212</v>
       </c>
       <c r="D100" t="n">
-        <v>3325</v>
+        <v>3305</v>
       </c>
       <c r="E100" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F100" t="n">
         <v>3.41</v>
       </c>
       <c r="G100" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="101">
@@ -2930,22 +2930,22 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C101" t="n">
         <v>3011</v>
       </c>
       <c r="D101" t="n">
-        <v>3124</v>
+        <v>3104</v>
       </c>
       <c r="E101" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F101" t="n">
         <v>3.2</v>
       </c>
       <c r="G101" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="102">
@@ -2955,22 +2955,22 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C102" t="n">
         <v>2686</v>
       </c>
       <c r="D102" t="n">
-        <v>2799</v>
+        <v>2779</v>
       </c>
       <c r="E102" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F102" t="n">
         <v>2.85</v>
       </c>
       <c r="G102" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="103">
@@ -2980,22 +2980,22 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C103" t="n">
         <v>2674</v>
       </c>
       <c r="D103" t="n">
-        <v>2787</v>
+        <v>2767</v>
       </c>
       <c r="E103" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F103" t="n">
         <v>2.84</v>
       </c>
       <c r="G103" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="104">
@@ -3005,22 +3005,22 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C104" t="n">
         <v>2086</v>
       </c>
       <c r="D104" t="n">
-        <v>2199</v>
+        <v>2179</v>
       </c>
       <c r="E104" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F104" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="G104" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="105">
@@ -3030,22 +3030,22 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C105" t="n">
         <v>1985</v>
       </c>
       <c r="D105" t="n">
-        <v>2098</v>
+        <v>2078</v>
       </c>
       <c r="E105" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F105" t="n">
         <v>2.11</v>
       </c>
       <c r="G105" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="106">
@@ -3055,22 +3055,22 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C106" t="n">
         <v>1825</v>
       </c>
       <c r="D106" t="n">
-        <v>1938</v>
+        <v>1918</v>
       </c>
       <c r="E106" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F106" t="n">
         <v>1.94</v>
       </c>
       <c r="G106" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="107">
@@ -3080,22 +3080,22 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C107" t="n">
         <v>1125</v>
       </c>
       <c r="D107" t="n">
-        <v>1238</v>
+        <v>1218</v>
       </c>
       <c r="E107" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F107" t="n">
         <v>1.19</v>
       </c>
       <c r="G107" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="108">
@@ -3105,22 +3105,22 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C108" t="n">
         <v>876</v>
       </c>
       <c r="D108" t="n">
-        <v>989</v>
+        <v>969</v>
       </c>
       <c r="E108" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F108" t="n">
         <v>0.93</v>
       </c>
       <c r="G108" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="109">
@@ -3130,22 +3130,22 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C109" t="n">
         <v>694</v>
       </c>
       <c r="D109" t="n">
-        <v>807</v>
+        <v>787</v>
       </c>
       <c r="E109" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F109" t="n">
         <v>0.74</v>
       </c>
       <c r="G109" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="110">
@@ -3155,22 +3155,22 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C110" t="n">
         <v>528</v>
       </c>
       <c r="D110" t="n">
-        <v>641</v>
+        <v>621</v>
       </c>
       <c r="E110" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F110" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="G110" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="111">
@@ -3180,22 +3180,22 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C111" t="n">
         <v>423</v>
       </c>
       <c r="D111" t="n">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="E111" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F111" t="n">
         <v>0.45</v>
       </c>
       <c r="G111" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="112">
@@ -3205,22 +3205,22 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C112" t="n">
         <v>427</v>
       </c>
       <c r="D112" t="n">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="E112" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F112" t="n">
         <v>0.45</v>
       </c>
       <c r="G112" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="113">
@@ -3230,22 +3230,22 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C113" t="n">
         <v>421</v>
       </c>
       <c r="D113" t="n">
-        <v>534</v>
+        <v>514</v>
       </c>
       <c r="E113" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F113" t="n">
         <v>0.45</v>
       </c>
       <c r="G113" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="114">
@@ -3255,22 +3255,22 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C114" t="n">
         <v>415</v>
       </c>
       <c r="D114" t="n">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="E114" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F114" t="n">
         <v>0.44</v>
       </c>
       <c r="G114" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="115">
@@ -3280,22 +3280,22 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C115" t="n">
         <v>398</v>
       </c>
       <c r="D115" t="n">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="E115" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F115" t="n">
         <v>0.42</v>
       </c>
       <c r="G115" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="116">
@@ -3305,22 +3305,22 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C116" t="n">
         <v>320</v>
       </c>
       <c r="D116" t="n">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="E116" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F116" t="n">
         <v>0.34</v>
       </c>
       <c r="G116" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="117">
@@ -3330,22 +3330,22 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C117" t="n">
         <v>305</v>
       </c>
       <c r="D117" t="n">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="E117" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F117" t="n">
         <v>0.32</v>
       </c>
       <c r="G117" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="118">
@@ -3355,22 +3355,22 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C118" t="n">
         <v>233</v>
       </c>
       <c r="D118" t="n">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="E118" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F118" t="n">
         <v>0.25</v>
       </c>
       <c r="G118" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="119">
@@ -3380,22 +3380,22 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C119" t="n">
         <v>142</v>
       </c>
       <c r="D119" t="n">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="E119" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F119" t="n">
         <v>0.15</v>
       </c>
       <c r="G119" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="120">
@@ -3405,22 +3405,22 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C120" t="n">
         <v>112</v>
       </c>
       <c r="D120" t="n">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="E120" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F120" t="n">
         <v>0.12</v>
       </c>
       <c r="G120" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="121">
@@ -3430,22 +3430,22 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C121" t="n">
         <v>92</v>
       </c>
       <c r="D121" t="n">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="E121" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F121" t="n">
         <v>0.1</v>
       </c>
       <c r="G121" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="122">
@@ -3455,22 +3455,22 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C122" t="n">
         <v>70</v>
       </c>
       <c r="D122" t="n">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="E122" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F122" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G122" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="123">
@@ -3480,22 +3480,22 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C123" t="n">
         <v>13</v>
       </c>
       <c r="D123" t="n">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="E123" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F123" t="n">
         <v>0.01</v>
       </c>
       <c r="G123" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="124">
@@ -3505,22 +3505,22 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C124" t="n">
         <v>13</v>
       </c>
       <c r="D124" t="n">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="E124" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F124" t="n">
         <v>0.01</v>
       </c>
       <c r="G124" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="125">
@@ -3530,22 +3530,22 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E125" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="126">
